--- a/research/traditional_assets/database/data/philippines/philippines_software_system_application.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_software_system_application.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.385</v>
+        <v>-0.312</v>
       </c>
       <c r="G2">
-        <v>-0.1686170212765958</v>
+        <v>-0.4135211267605634</v>
       </c>
       <c r="H2">
-        <v>-0.2356382978723404</v>
+        <v>-0.4507042253521127</v>
       </c>
       <c r="I2">
-        <v>-0.1871638919906419</v>
+        <v>-0.7429746229114025</v>
       </c>
       <c r="J2">
-        <v>-0.1871638919906419</v>
+        <v>-0.7429746229114025</v>
       </c>
       <c r="K2">
-        <v>-0.206</v>
+        <v>-1.24</v>
       </c>
       <c r="L2">
-        <v>-0.05478723404255319</v>
+        <v>-0.3492957746478874</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.35</v>
+        <v>1.97</v>
       </c>
       <c r="V2">
-        <v>0.1380368098159509</v>
+        <v>0.2277456647398844</v>
       </c>
       <c r="W2">
-        <v>-0.09716981132075471</v>
+        <v>-0.5166666666666667</v>
       </c>
       <c r="X2">
-        <v>0.1893194260971128</v>
+        <v>0.161045377517247</v>
       </c>
       <c r="Y2">
-        <v>-0.2864892374178675</v>
+        <v>-0.6777120441839137</v>
       </c>
       <c r="Z2">
-        <v>0.811800264841533</v>
+        <v>1.062301894470778</v>
       </c>
       <c r="AA2">
-        <v>-0.1519396970867752</v>
+        <v>-0.7892633494624945</v>
       </c>
       <c r="AB2">
-        <v>0.1562669411388687</v>
+        <v>0.130738783555587</v>
       </c>
       <c r="AC2">
-        <v>-0.3082066382256439</v>
+        <v>-0.9200021330180815</v>
       </c>
       <c r="AD2">
-        <v>3.11</v>
+        <v>3.4</v>
       </c>
       <c r="AE2">
-        <v>0.01868116942406726</v>
+        <v>0.00279955667739284</v>
       </c>
       <c r="AF2">
-        <v>3.128681169424067</v>
+        <v>3.402799556677393</v>
       </c>
       <c r="AG2">
-        <v>1.778681169424067</v>
+        <v>1.432799556677393</v>
       </c>
       <c r="AH2">
-        <v>0.2423703187305273</v>
+        <v>0.2823244127371389</v>
       </c>
       <c r="AI2">
-        <v>0.8973235628369385</v>
+        <v>1.434086392633307</v>
       </c>
       <c r="AJ2">
-        <v>0.153882708879381</v>
+        <v>0.1421033462604652</v>
       </c>
       <c r="AK2">
-        <v>0.8324504352249721</v>
+        <v>3.557103112268171</v>
       </c>
       <c r="AL2">
-        <v>0.144</v>
+        <v>0.114</v>
       </c>
       <c r="AM2">
-        <v>0.139</v>
+        <v>-0.02899999999999998</v>
       </c>
       <c r="AN2">
-        <v>-4.092105263157895</v>
+        <v>-1.270078446021666</v>
       </c>
       <c r="AO2">
-        <v>-5</v>
+        <v>-23.15789473684211</v>
       </c>
       <c r="AP2">
-        <v>-2.340369959768509</v>
+        <v>-0.5352258336486337</v>
       </c>
       <c r="AQ2">
-        <v>-5.179856115107914</v>
+        <v>91.03448275862074</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.385</v>
+        <v>-0.312</v>
       </c>
       <c r="G3">
-        <v>-0.1686170212765958</v>
+        <v>-0.4135211267605634</v>
       </c>
       <c r="H3">
-        <v>-0.2356382978723404</v>
+        <v>-0.4507042253521127</v>
       </c>
       <c r="I3">
-        <v>-0.1871638919906419</v>
+        <v>-0.7429746229114025</v>
       </c>
       <c r="J3">
-        <v>-0.1871638919906419</v>
+        <v>-0.7429746229114025</v>
       </c>
       <c r="K3">
-        <v>-0.206</v>
+        <v>-1.24</v>
       </c>
       <c r="L3">
-        <v>-0.05478723404255319</v>
+        <v>-0.3492957746478874</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.35</v>
+        <v>1.97</v>
       </c>
       <c r="V3">
-        <v>0.1380368098159509</v>
+        <v>0.2277456647398844</v>
       </c>
       <c r="W3">
-        <v>-0.09716981132075471</v>
+        <v>-0.5166666666666667</v>
       </c>
       <c r="X3">
-        <v>0.1893194260971128</v>
+        <v>0.161045377517247</v>
       </c>
       <c r="Y3">
-        <v>-0.2864892374178675</v>
+        <v>-0.6777120441839137</v>
       </c>
       <c r="Z3">
-        <v>0.811800264841533</v>
+        <v>1.062301894470778</v>
       </c>
       <c r="AA3">
-        <v>-0.1519396970867752</v>
+        <v>-0.7892633494624945</v>
       </c>
       <c r="AB3">
-        <v>0.1562669411388687</v>
+        <v>0.130738783555587</v>
       </c>
       <c r="AC3">
-        <v>-0.3082066382256439</v>
+        <v>-0.9200021330180815</v>
       </c>
       <c r="AD3">
-        <v>3.11</v>
+        <v>3.4</v>
       </c>
       <c r="AE3">
-        <v>0.01868116942406726</v>
+        <v>0.00279955667739284</v>
       </c>
       <c r="AF3">
-        <v>3.128681169424067</v>
+        <v>3.402799556677393</v>
       </c>
       <c r="AG3">
-        <v>1.778681169424067</v>
+        <v>1.432799556677393</v>
       </c>
       <c r="AH3">
-        <v>0.2423703187305273</v>
+        <v>0.2823244127371389</v>
       </c>
       <c r="AI3">
-        <v>0.8973235628369385</v>
+        <v>1.434086392633307</v>
       </c>
       <c r="AJ3">
-        <v>0.153882708879381</v>
+        <v>0.1421033462604652</v>
       </c>
       <c r="AK3">
-        <v>0.8324504352249721</v>
+        <v>3.557103112268171</v>
       </c>
       <c r="AL3">
-        <v>0.144</v>
+        <v>0.114</v>
       </c>
       <c r="AM3">
-        <v>0.139</v>
+        <v>-0.02899999999999998</v>
       </c>
       <c r="AN3">
-        <v>-4.092105263157895</v>
+        <v>-1.270078446021666</v>
       </c>
       <c r="AO3">
-        <v>-5</v>
+        <v>-23.15789473684211</v>
       </c>
       <c r="AP3">
-        <v>-2.340369959768509</v>
+        <v>-0.5352258336486337</v>
       </c>
       <c r="AQ3">
-        <v>-5.179856115107914</v>
+        <v>91.03448275862074</v>
       </c>
     </row>
   </sheetData>
